--- a/exports/trend_1d/ATHERENERG_full_report.xlsx
+++ b/exports/trend_1d/ATHERENERG_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.47</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H2" t="n">
-        <v>667.15</v>
+        <v>633.85</v>
       </c>
       <c r="I2" t="n">
         <v>639.212186409158</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K2" t="n">
-        <v>107.9</v>
+        <v>97.52</v>
       </c>
       <c r="L2" t="n">
         <v>6.2</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>19.31</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H3" t="n">
-        <v>731.9</v>
+        <v>754.75</v>
       </c>
       <c r="I3" t="n">
         <v>734.9388904635975</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.47</v>
+        <v>-19.07</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>19.9</v>
       </c>
       <c r="M3" t="n">
         <v>2.31</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>13.36</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H4" t="n">
-        <v>672.7</v>
+        <v>633.3</v>
       </c>
       <c r="I4" t="n">
         <v>654.8450301101323</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.87</v>
+        <v>-16.09</v>
       </c>
       <c r="L4" t="n">
-        <v>12.23</v>
+        <v>17.19</v>
       </c>
       <c r="M4" t="n">
         <v>0.07000000000000001</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>18.36</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H5" t="n">
-        <v>675.9</v>
+        <v>696.05</v>
       </c>
       <c r="I5" t="n">
         <v>686.0421086020899</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.73</v>
+        <v>-9.91</v>
       </c>
       <c r="L5" t="n">
-        <v>8.140000000000001</v>
+        <v>11.23</v>
       </c>
       <c r="M5" t="n">
         <v>7.82</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.48</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H6" t="n">
-        <v>1543.8</v>
+        <v>1499.4</v>
       </c>
       <c r="I6" t="n">
         <v>1509.509586432074</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K6" t="n">
-        <v>121.79</v>
+        <v>115.42</v>
       </c>
       <c r="L6" t="n">
         <v>6.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>14.56</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H7" t="n">
-        <v>1575</v>
+        <v>1674</v>
       </c>
       <c r="I7" t="n">
         <v>1575.353017702373</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.04</v>
+        <v>-11.64</v>
       </c>
       <c r="L7" t="n">
-        <v>8.24</v>
+        <v>13.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.68</v>
+        <v>2.03</v>
       </c>
       <c r="N7" t="n">
         <v>14.13</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -900,6 +995,12 @@
       <c r="Q8" t="n">
         <v>2</v>
       </c>
+      <c r="R8" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1642,7 +1743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6">
@@ -1652,7 +1753,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="7">
@@ -1662,7 +1763,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
@@ -1672,7 +1773,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1682,7 +1783,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139.5</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="10">
@@ -1692,7 +1793,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>200.5</v>
       </c>
     </row>
     <row r="11">
@@ -1732,7 +1833,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.93</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="15">
@@ -1742,7 +1843,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.94</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="16">
@@ -1752,7 +1853,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-9.08</v>
+        <v>-13.54</v>
       </c>
     </row>
     <row r="17">
@@ -1762,7 +1863,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>121.79</v>
+        <v>115.42</v>
       </c>
     </row>
     <row r="18">
@@ -1782,7 +1883,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.890000000000001</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="20">
@@ -1792,7 +1893,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.19</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="21">
@@ -1802,7 +1903,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="22">
@@ -1822,7 +1923,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1832,7 +1933,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="25">
